--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>136261248</v>
       </c>
       <c r="B13" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>136050898</v>
       </c>
       <c r="B95" t="n">
-        <v>96758</v>
+        <v>96759</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>136261248</v>
       </c>
       <c r="B13" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>136050898</v>
       </c>
       <c r="B95" t="n">
-        <v>96759</v>
+        <v>96772</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>136239010</v>
       </c>
       <c r="B101" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>136050860</v>
       </c>
       <c r="B220" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>136261248</v>
       </c>
       <c r="B13" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>136050898</v>
       </c>
       <c r="B95" t="n">
-        <v>96772</v>
+        <v>96773</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>136261248</v>
       </c>
       <c r="B13" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>136050898</v>
       </c>
       <c r="B95" t="n">
-        <v>96773</v>
+        <v>96776</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>136261248</v>
       </c>
       <c r="B13" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>136050898</v>
       </c>
       <c r="B95" t="n">
-        <v>96776</v>
+        <v>96777</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>136261248</v>
       </c>
       <c r="B13" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>136777548</v>
       </c>
       <c r="B97" t="n">
-        <v>93422</v>
+        <v>93427</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>136239010</v>
       </c>
       <c r="B102" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>136777576</v>
       </c>
       <c r="B103" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>136261248</v>
       </c>
       <c r="B13" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>136777548</v>
       </c>
       <c r="B97" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>137014659</v>
       </c>
       <c r="B96" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>136777548</v>
       </c>
       <c r="B106" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>137015674</v>
       </c>
       <c r="B124" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>137015708</v>
       </c>
       <c r="B125" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>137015557</v>
       </c>
       <c r="B151" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>137015586</v>
       </c>
       <c r="B152" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>137015628</v>
       </c>
       <c r="B153" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>137015943</v>
       </c>
       <c r="B203" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>137015962</v>
       </c>
       <c r="B204" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>137015745</v>
       </c>
       <c r="B272" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>137015790</v>
       </c>
       <c r="B273" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>137016225</v>
       </c>
       <c r="B279" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>137015901</v>
       </c>
       <c r="B282" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>137016008</v>
       </c>
       <c r="B283" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>137016050</v>
       </c>
       <c r="B284" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>137016038</v>
       </c>
       <c r="B293" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>137016093</v>
       </c>
       <c r="B294" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>137016208</v>
       </c>
       <c r="B295" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>137014659</v>
       </c>
       <c r="B96" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>136777548</v>
       </c>
       <c r="B106" t="n">
-        <v>93431</v>
+        <v>93433</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -12876,7 +12876,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -14133,7 +14133,7 @@
         <v>137015674</v>
       </c>
       <c r="B124" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>137015708</v>
       </c>
       <c r="B125" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>137015557</v>
       </c>
       <c r="B151" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>137015586</v>
       </c>
       <c r="B152" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>137015628</v>
       </c>
       <c r="B153" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>137015943</v>
       </c>
       <c r="B203" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>137015962</v>
       </c>
       <c r="B204" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>137015745</v>
       </c>
       <c r="B272" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>137015790</v>
       </c>
       <c r="B273" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>137016225</v>
       </c>
       <c r="B279" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>137015901</v>
       </c>
       <c r="B282" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>137016008</v>
       </c>
       <c r="B283" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>137016050</v>
       </c>
       <c r="B284" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>137016038</v>
       </c>
       <c r="B293" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>137016093</v>
       </c>
       <c r="B294" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>137016208</v>
       </c>
       <c r="B295" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -12207,7 +12207,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -12876,7 +12876,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>137014659</v>
       </c>
       <c r="B96" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>136777548</v>
       </c>
       <c r="B106" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>137015674</v>
       </c>
       <c r="B124" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>137015708</v>
       </c>
       <c r="B125" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>137015557</v>
       </c>
       <c r="B151" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>137015586</v>
       </c>
       <c r="B152" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>137015628</v>
       </c>
       <c r="B153" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>137015943</v>
       </c>
       <c r="B203" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>137015962</v>
       </c>
       <c r="B204" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>137015745</v>
       </c>
       <c r="B272" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>137015790</v>
       </c>
       <c r="B273" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>137016225</v>
       </c>
       <c r="B279" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>137015901</v>
       </c>
       <c r="B282" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>137016008</v>
       </c>
       <c r="B283" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>137016050</v>
       </c>
       <c r="B284" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>137016038</v>
       </c>
       <c r="B293" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>137016093</v>
       </c>
       <c r="B294" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>137016208</v>
       </c>
       <c r="B295" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>137014659</v>
       </c>
       <c r="B96" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>136777548</v>
       </c>
       <c r="B106" t="n">
-        <v>93434</v>
+        <v>93440</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>137015674</v>
       </c>
       <c r="B124" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>137015708</v>
       </c>
       <c r="B125" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>137015557</v>
       </c>
       <c r="B151" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>137015586</v>
       </c>
       <c r="B152" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>137015628</v>
       </c>
       <c r="B153" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>137015943</v>
       </c>
       <c r="B203" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>137015962</v>
       </c>
       <c r="B204" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>137015745</v>
       </c>
       <c r="B272" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>137015790</v>
       </c>
       <c r="B273" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>137016225</v>
       </c>
       <c r="B279" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>137015901</v>
       </c>
       <c r="B282" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>137016008</v>
       </c>
       <c r="B283" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>137016050</v>
       </c>
       <c r="B284" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>137016038</v>
       </c>
       <c r="B293" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>137016093</v>
       </c>
       <c r="B294" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>137016208</v>
       </c>
       <c r="B295" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>137014659</v>
       </c>
       <c r="B96" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>136777548</v>
       </c>
       <c r="B106" t="n">
-        <v>93440</v>
+        <v>93444</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>137015674</v>
       </c>
       <c r="B124" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>137015708</v>
       </c>
       <c r="B125" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>137015557</v>
       </c>
       <c r="B151" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>137015586</v>
       </c>
       <c r="B152" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>137015628</v>
       </c>
       <c r="B153" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>137015943</v>
       </c>
       <c r="B203" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>137015962</v>
       </c>
       <c r="B204" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>137015745</v>
       </c>
       <c r="B272" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>137015790</v>
       </c>
       <c r="B273" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>137016225</v>
       </c>
       <c r="B279" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>137015901</v>
       </c>
       <c r="B282" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>137016008</v>
       </c>
       <c r="B283" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>137016050</v>
       </c>
       <c r="B284" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>137016038</v>
       </c>
       <c r="B293" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>137016093</v>
       </c>
       <c r="B294" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>137016208</v>
       </c>
       <c r="B295" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>137014659</v>
       </c>
       <c r="B96" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>136777548</v>
       </c>
       <c r="B106" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>137015674</v>
       </c>
       <c r="B124" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>137015708</v>
       </c>
       <c r="B125" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>137015557</v>
       </c>
       <c r="B151" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>137015586</v>
       </c>
       <c r="B152" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>137015628</v>
       </c>
       <c r="B153" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>137015943</v>
       </c>
       <c r="B203" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>137015962</v>
       </c>
       <c r="B204" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>137015745</v>
       </c>
       <c r="B272" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>137015790</v>
       </c>
       <c r="B273" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>137016225</v>
       </c>
       <c r="B279" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>137015901</v>
       </c>
       <c r="B282" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>137016008</v>
       </c>
       <c r="B283" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>137016050</v>
       </c>
       <c r="B284" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>137016038</v>
       </c>
       <c r="B293" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>137016093</v>
       </c>
       <c r="B294" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>137016208</v>
       </c>
       <c r="B295" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>137015523</v>
       </c>
       <c r="B46" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>137014659</v>
       </c>
       <c r="B96" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>136777548</v>
       </c>
       <c r="B106" t="n">
-        <v>93446</v>
+        <v>93459</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>136777576</v>
       </c>
       <c r="B112" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>137018446</v>
       </c>
       <c r="B113" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>137015674</v>
       </c>
       <c r="B124" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>137015708</v>
       </c>
       <c r="B125" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>137015557</v>
       </c>
       <c r="B151" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>137015586</v>
       </c>
       <c r="B152" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>137015628</v>
       </c>
       <c r="B153" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>137015943</v>
       </c>
       <c r="B203" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>137015962</v>
       </c>
       <c r="B204" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -26493,7 +26493,7 @@
         <v>137016499</v>
       </c>
       <c r="B239" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>137015745</v>
       </c>
       <c r="B272" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>137015790</v>
       </c>
       <c r="B273" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>137016225</v>
       </c>
       <c r="B279" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>137015901</v>
       </c>
       <c r="B282" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>137016008</v>
       </c>
       <c r="B283" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>137016050</v>
       </c>
       <c r="B284" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>137016038</v>
       </c>
       <c r="B293" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>137016093</v>
       </c>
       <c r="B294" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>137016208</v>
       </c>
       <c r="B295" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>137015523</v>
       </c>
       <c r="B46" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5618,11 +5618,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -9480,7 +9476,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9586,7 +9582,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9692,7 +9688,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9798,7 +9794,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10982,7 +10978,7 @@
         <v>137014659</v>
       </c>
       <c r="B96" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12110,7 +12106,7 @@
         <v>136777548</v>
       </c>
       <c r="B106" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12207,7 +12203,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -12774,7 +12770,7 @@
         <v>136777576</v>
       </c>
       <c r="B112" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12800,11 +12796,7 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Norrby torp, Tyresta, Srm</t>
@@ -12876,7 +12868,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -12891,7 +12883,7 @@
         <v>137018446</v>
       </c>
       <c r="B113" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12919,11 +12911,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -14133,7 +14121,7 @@
         <v>137015674</v>
       </c>
       <c r="B124" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14239,7 +14227,7 @@
         <v>137015708</v>
       </c>
       <c r="B125" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17035,7 +17023,7 @@
         <v>137015557</v>
       </c>
       <c r="B151" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17141,7 +17129,7 @@
         <v>137015586</v>
       </c>
       <c r="B152" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17247,7 +17235,7 @@
         <v>137015628</v>
       </c>
       <c r="B153" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -22590,7 +22578,7 @@
         <v>137015943</v>
       </c>
       <c r="B203" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22696,7 +22684,7 @@
         <v>137015962</v>
       </c>
       <c r="B204" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -26493,7 +26481,7 @@
         <v>137016499</v>
       </c>
       <c r="B239" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -26521,11 +26509,7 @@
       <c r="I239" t="inlineStr"/>
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M239" t="inlineStr"/>
       <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
@@ -30058,7 +30042,7 @@
         <v>137015745</v>
       </c>
       <c r="B272" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30164,7 +30148,7 @@
         <v>137015790</v>
       </c>
       <c r="B273" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30826,7 +30810,7 @@
         <v>137016225</v>
       </c>
       <c r="B279" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31148,7 +31132,7 @@
         <v>137015901</v>
       </c>
       <c r="B282" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31254,7 +31238,7 @@
         <v>137016008</v>
       </c>
       <c r="B283" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31360,7 +31344,7 @@
         <v>137016050</v>
       </c>
       <c r="B284" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32323,7 +32307,7 @@
         <v>137016038</v>
       </c>
       <c r="B293" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -32429,7 +32413,7 @@
         <v>137016093</v>
       </c>
       <c r="B294" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -32535,7 +32519,7 @@
         <v>137016208</v>
       </c>
       <c r="B295" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>137014659</v>
       </c>
       <c r="B96" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>136777548</v>
       </c>
       <c r="B106" t="n">
-        <v>93460</v>
+        <v>93463</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -12868,7 +12868,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -14121,7 +14121,7 @@
         <v>137015674</v>
       </c>
       <c r="B124" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>137015708</v>
       </c>
       <c r="B125" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>137015557</v>
       </c>
       <c r="B151" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>137015586</v>
       </c>
       <c r="B152" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>137015628</v>
       </c>
       <c r="B153" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>137015943</v>
       </c>
       <c r="B203" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>137015962</v>
       </c>
       <c r="B204" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>137015745</v>
       </c>
       <c r="B272" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>137015790</v>
       </c>
       <c r="B273" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>137016225</v>
       </c>
       <c r="B279" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>137015901</v>
       </c>
       <c r="B282" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>137016008</v>
       </c>
       <c r="B283" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>137016050</v>
       </c>
       <c r="B284" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>137016038</v>
       </c>
       <c r="B293" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>137016093</v>
       </c>
       <c r="B294" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>137016208</v>
       </c>
       <c r="B295" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>137015523</v>
       </c>
       <c r="B46" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>137014659</v>
       </c>
       <c r="B96" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>136777548</v>
       </c>
       <c r="B106" t="n">
-        <v>93463</v>
+        <v>93473</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>136777576</v>
       </c>
       <c r="B112" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>137018446</v>
       </c>
       <c r="B113" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>137015674</v>
       </c>
       <c r="B124" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>137015708</v>
       </c>
       <c r="B125" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>137015557</v>
       </c>
       <c r="B151" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>137015586</v>
       </c>
       <c r="B152" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>137015628</v>
       </c>
       <c r="B153" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>137015943</v>
       </c>
       <c r="B203" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>137015962</v>
       </c>
       <c r="B204" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>137016499</v>
       </c>
       <c r="B239" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>137015745</v>
       </c>
       <c r="B272" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>137015790</v>
       </c>
       <c r="B273" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>137016225</v>
       </c>
       <c r="B279" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>137015901</v>
       </c>
       <c r="B282" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>137016008</v>
       </c>
       <c r="B283" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>137016050</v>
       </c>
       <c r="B284" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>137016038</v>
       </c>
       <c r="B293" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>137016093</v>
       </c>
       <c r="B294" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>137016208</v>
       </c>
       <c r="B295" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>137014659</v>
       </c>
       <c r="B96" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>136777548</v>
       </c>
       <c r="B106" t="n">
-        <v>93473</v>
+        <v>93474</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>137015674</v>
       </c>
       <c r="B124" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>137015708</v>
       </c>
       <c r="B125" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>137015557</v>
       </c>
       <c r="B151" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>137015586</v>
       </c>
       <c r="B152" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>137015628</v>
       </c>
       <c r="B153" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>137015943</v>
       </c>
       <c r="B203" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>137015962</v>
       </c>
       <c r="B204" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>137015745</v>
       </c>
       <c r="B272" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>137015790</v>
       </c>
       <c r="B273" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>137016225</v>
       </c>
       <c r="B279" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>137015901</v>
       </c>
       <c r="B282" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>137016008</v>
       </c>
       <c r="B283" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>137016050</v>
       </c>
       <c r="B284" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>137016038</v>
       </c>
       <c r="B293" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>137016093</v>
       </c>
       <c r="B294" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>137016208</v>
       </c>
       <c r="B295" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>137015523</v>
       </c>
       <c r="B46" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>137014659</v>
       </c>
       <c r="B96" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>136777548</v>
       </c>
       <c r="B106" t="n">
-        <v>93474</v>
+        <v>93479</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>136777576</v>
       </c>
       <c r="B112" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>137018446</v>
       </c>
       <c r="B113" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>137015674</v>
       </c>
       <c r="B124" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>137015708</v>
       </c>
       <c r="B125" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>137015557</v>
       </c>
       <c r="B151" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>137015586</v>
       </c>
       <c r="B152" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>137015628</v>
       </c>
       <c r="B153" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>137015943</v>
       </c>
       <c r="B203" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>137015962</v>
       </c>
       <c r="B204" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>137016499</v>
       </c>
       <c r="B239" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>137015745</v>
       </c>
       <c r="B272" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>137015790</v>
       </c>
       <c r="B273" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>137016225</v>
       </c>
       <c r="B279" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>137015901</v>
       </c>
       <c r="B282" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>137016008</v>
       </c>
       <c r="B283" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>137016050</v>
       </c>
       <c r="B284" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>137016038</v>
       </c>
       <c r="B293" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>137016093</v>
       </c>
       <c r="B294" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>137016208</v>
       </c>
       <c r="B295" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>137014659</v>
       </c>
       <c r="B96" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>136777548</v>
       </c>
       <c r="B106" t="n">
-        <v>93479</v>
+        <v>93481</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>137015674</v>
       </c>
       <c r="B124" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>137015708</v>
       </c>
       <c r="B125" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>137015557</v>
       </c>
       <c r="B151" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>137015586</v>
       </c>
       <c r="B152" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>137015628</v>
       </c>
       <c r="B153" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>137015943</v>
       </c>
       <c r="B203" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>137015962</v>
       </c>
       <c r="B204" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>137015745</v>
       </c>
       <c r="B272" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>137015790</v>
       </c>
       <c r="B273" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>137016225</v>
       </c>
       <c r="B279" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>137015901</v>
       </c>
       <c r="B282" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>137016008</v>
       </c>
       <c r="B283" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>137016050</v>
       </c>
       <c r="B284" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>137016038</v>
       </c>
       <c r="B293" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>137016093</v>
       </c>
       <c r="B294" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>137016208</v>
       </c>
       <c r="B295" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>137015523</v>
       </c>
       <c r="B46" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>137014659</v>
       </c>
       <c r="B96" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>137018446</v>
       </c>
       <c r="B113" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>137015674</v>
       </c>
       <c r="B124" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>137015708</v>
       </c>
       <c r="B125" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>137015557</v>
       </c>
       <c r="B151" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>137015586</v>
       </c>
       <c r="B152" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>137015628</v>
       </c>
       <c r="B153" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>137015943</v>
       </c>
       <c r="B203" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>137015962</v>
       </c>
       <c r="B204" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>137016499</v>
       </c>
       <c r="B239" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>137015745</v>
       </c>
       <c r="B272" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>137015790</v>
       </c>
       <c r="B273" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>137016225</v>
       </c>
       <c r="B279" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>137015901</v>
       </c>
       <c r="B282" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>137016008</v>
       </c>
       <c r="B283" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>137016050</v>
       </c>
       <c r="B284" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>137016038</v>
       </c>
       <c r="B293" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>137016093</v>
       </c>
       <c r="B294" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>137016208</v>
       </c>
       <c r="B295" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>128811657</v>
       </c>
       <c r="B91" t="n">
-        <v>93490</v>
+        <v>93502</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>137014659</v>
       </c>
       <c r="B97" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>137015674</v>
       </c>
       <c r="B125" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>137015708</v>
       </c>
       <c r="B126" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>137015557</v>
       </c>
       <c r="B152" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>137015586</v>
       </c>
       <c r="B153" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>137015628</v>
       </c>
       <c r="B154" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>128795040</v>
       </c>
       <c r="B159" t="n">
-        <v>93490</v>
+        <v>93502</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>137015943</v>
       </c>
       <c r="B205" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>137015962</v>
       </c>
       <c r="B206" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>137015745</v>
       </c>
       <c r="B274" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>137015790</v>
       </c>
       <c r="B275" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>137016225</v>
       </c>
       <c r="B281" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>137015901</v>
       </c>
       <c r="B284" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -31450,7 +31450,7 @@
         <v>137016008</v>
       </c>
       <c r="B285" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>137016050</v>
       </c>
       <c r="B286" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>137016038</v>
       </c>
       <c r="B295" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>137016093</v>
       </c>
       <c r="B296" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>137016208</v>
       </c>
       <c r="B297" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>128811657</v>
       </c>
       <c r="B91" t="n">
-        <v>93502</v>
+        <v>93503</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>137014659</v>
       </c>
       <c r="B97" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>137015674</v>
       </c>
       <c r="B125" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>137015708</v>
       </c>
       <c r="B126" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>137015557</v>
       </c>
       <c r="B152" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>137015586</v>
       </c>
       <c r="B153" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>137015628</v>
       </c>
       <c r="B154" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>128795040</v>
       </c>
       <c r="B159" t="n">
-        <v>93502</v>
+        <v>93503</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>137015943</v>
       </c>
       <c r="B205" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>137015962</v>
       </c>
       <c r="B206" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>137015745</v>
       </c>
       <c r="B274" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>137015790</v>
       </c>
       <c r="B275" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>137016225</v>
       </c>
       <c r="B281" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>137015901</v>
       </c>
       <c r="B284" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -31450,7 +31450,7 @@
         <v>137016008</v>
       </c>
       <c r="B285" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>137016050</v>
       </c>
       <c r="B286" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>137016038</v>
       </c>
       <c r="B295" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>137016093</v>
       </c>
       <c r="B296" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>137016208</v>
       </c>
       <c r="B297" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>128811657</v>
       </c>
       <c r="B91" t="n">
-        <v>93503</v>
+        <v>93506</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>137014659</v>
       </c>
       <c r="B97" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>137015674</v>
       </c>
       <c r="B125" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>137015708</v>
       </c>
       <c r="B126" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>137015557</v>
       </c>
       <c r="B152" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>137015586</v>
       </c>
       <c r="B153" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>137015628</v>
       </c>
       <c r="B154" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>128795040</v>
       </c>
       <c r="B159" t="n">
-        <v>93503</v>
+        <v>93506</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>137015943</v>
       </c>
       <c r="B205" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>137015962</v>
       </c>
       <c r="B206" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>137015745</v>
       </c>
       <c r="B274" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>137015790</v>
       </c>
       <c r="B275" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>137016225</v>
       </c>
       <c r="B281" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>137015901</v>
       </c>
       <c r="B284" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -31450,7 +31450,7 @@
         <v>137016008</v>
       </c>
       <c r="B285" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>137016050</v>
       </c>
       <c r="B286" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>137016038</v>
       </c>
       <c r="B295" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>137016093</v>
       </c>
       <c r="B296" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>137016208</v>
       </c>
       <c r="B297" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -4165,7 +4165,7 @@
         <v>137015230</v>
       </c>
       <c r="B33" t="n">
-        <v>97020</v>
+        <v>97023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>137015423</v>
       </c>
       <c r="B39" t="n">
-        <v>92207</v>
+        <v>92210</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>137015493</v>
       </c>
       <c r="B42" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>137015523</v>
       </c>
       <c r="B46" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>137014646</v>
       </c>
       <c r="B82" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>137014688</v>
       </c>
       <c r="B83" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>137014697</v>
       </c>
       <c r="B84" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137014755</v>
       </c>
       <c r="B85" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>128811657</v>
       </c>
       <c r="B91" t="n">
-        <v>93506</v>
+        <v>93510</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>137014659</v>
       </c>
       <c r="B97" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>137519745</v>
       </c>
       <c r="B107" t="n">
-        <v>92200</v>
+        <v>92203</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>137018446</v>
       </c>
       <c r="B115" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>137015674</v>
       </c>
       <c r="B126" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>137015708</v>
       </c>
       <c r="B127" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>137015557</v>
       </c>
       <c r="B153" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>137015586</v>
       </c>
       <c r="B154" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>137015628</v>
       </c>
       <c r="B155" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         <v>128795040</v>
       </c>
       <c r="B160" t="n">
-        <v>93506</v>
+        <v>93510</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>137015943</v>
       </c>
       <c r="B206" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>137015962</v>
       </c>
       <c r="B207" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>137519184</v>
       </c>
       <c r="B225" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>137510834</v>
       </c>
       <c r="B233" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>137519037</v>
       </c>
       <c r="B234" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>137016499</v>
       </c>
       <c r="B245" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>137519065</v>
       </c>
       <c r="B246" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>137015745</v>
       </c>
       <c r="B279" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>137015790</v>
       </c>
       <c r="B280" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>137016225</v>
       </c>
       <c r="B286" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>137519327</v>
       </c>
       <c r="B287" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>137015901</v>
       </c>
       <c r="B290" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>137016008</v>
       </c>
       <c r="B291" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>137016050</v>
       </c>
       <c r="B292" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>137016038</v>
       </c>
       <c r="B301" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>137016093</v>
       </c>
       <c r="B302" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>137016208</v>
       </c>
       <c r="B303" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -33490,7 +33490,7 @@
         <v>137519301</v>
       </c>
       <c r="B304" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -33808,7 +33808,7 @@
         <v>137519290</v>
       </c>
       <c r="B307" t="n">
-        <v>92207</v>
+        <v>92210</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>137519307</v>
       </c>
       <c r="B314" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
